--- a/Collections/EURO/Latvia/#EURO#Latvia#Commemorative#[2014-present]#UNC.xlsx
+++ b/Collections/EURO/Latvia/#EURO#Latvia#Commemorative#[2014-present]#UNC.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Latvia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A6EBA7-1AE8-4222-912E-F01C70A175D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F1E0F5-5A75-48F2-A4E2-D952B34E9411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="20320" yWindow="8630" windowWidth="21070" windowHeight="14960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2€" sheetId="1" r:id="rId1"/>
     <sheet name="Links" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2€'!$B$2:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2€'!$B$2:$I$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,11 +43,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Илюшин Алексей</author>
     <author>Пользователь Windows</author>
   </authors>
   <commentList>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{2A050B41-129B-485F-8B3C-51C4F073FFFD}">
       <text>
         <r>
           <rPr>
@@ -58,16 +57,12 @@
             <family val="2"/>
             <charset val="204"/>
           </rPr>
-          <t>German mints:
-Staatliche Münzen Baden-Württemberg 
-(Stuttgart mint)
-+
-Staatliche Münze Karlsruhe
-(Karlsruhe mint)</t>
+          <t>Staatliche Münzen Baden-Württemberg 
+(Stuttgart mint)</t>
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -83,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="1" shapeId="0" xr:uid="{353C4EC3-9D0F-4086-BBE3-546332E42A4D}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{353C4EC3-9D0F-4086-BBE3-546332E42A4D}">
       <text>
         <r>
           <rPr>
@@ -99,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{606A0EA8-C46E-4AAC-9030-ADD315C8AF3C}">
       <text>
         <r>
           <rPr>
@@ -110,16 +105,28 @@
             <family val="2"/>
             <charset val="204"/>
           </rPr>
-          <t>German mints:
-Staatliche Münzen Baden-Württemberg 
-(Stuttgart mint)
-+
-Staatliche Münze Karlsruhe
-(Karlsruhe mint)</t>
+          <t>Istituto Poligrafico e Zecca dello Stato
+(Rome mint)</t>
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{3172DBF3-E3D8-46AD-A1B1-34556E2649DA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Staatliche Münzen Baden-Württemberg 
+(Stuttgart mint)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -135,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="1" shapeId="0" xr:uid="{D0586513-4B23-4DD6-87E2-31F881C55861}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{D0586513-4B23-4DD6-87E2-31F881C55861}">
       <text>
         <r>
           <rPr>
@@ -151,12 +158,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{D2A60C42-AEB0-4226-93FB-2FECE8C2C119}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Istituto Poligrafico e Zecca dello Stato
+(Rome mint)</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="66">
   <si>
     <t>Year</t>
   </si>
@@ -215,9 +238,6 @@
     <t>High convenience set of tables table of actual coins with photos</t>
   </si>
   <si>
-    <t>F+G</t>
-  </si>
-  <si>
     <t>LT</t>
   </si>
   <si>
@@ -351,6 +371,12 @@
   </si>
   <si>
     <t>Subtype_2#Special_marks_1</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>IT</t>
   </si>
 </sst>
 </file>
@@ -459,7 +485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -555,6 +581,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -642,6 +677,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -650,15 +694,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1160,19 +1195,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="7" customWidth="1"/>
     <col min="2" max="2" width="50.6328125" style="7" customWidth="1"/>
     <col min="3" max="5" width="33.6328125" style="7" customWidth="1"/>
-    <col min="6" max="8" width="12.6328125" style="7" customWidth="1"/>
-    <col min="9" max="11" width="3.6328125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="9.1796875" style="1"/>
+    <col min="6" max="9" width="12.6328125" style="7" customWidth="1"/>
+    <col min="10" max="13" width="3.6328125" style="7" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" style="7" customWidth="1"/>
+    <col min="15" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1182,68 +1217,76 @@
       </c>
       <c r="D1" s="28"/>
       <c r="E1" s="29"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="34"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="30" t="s">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="2"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18">
         <v>2014</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>4</v>
@@ -1251,75 +1294,87 @@
       <c r="H3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="17">
         <v>1</v>
       </c>
-      <c r="J3" s="17" t="s">
-        <v>4</v>
-      </c>
       <c r="K3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="21" t="str">
-        <f>IF(OR(AND(I3&gt;1,I3&lt;&gt;"-"),AND(J3&gt;1,J3&lt;&gt;"-"),AND(K3&gt;1,K3&lt;&gt;"-")),"Can exchange","")</f>
+      <c r="L3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="21" t="str">
+        <f>IF(OR(AND(J3&gt;1,J3&lt;&gt;"-"),AND(K3&gt;1,K3&lt;&gt;"-"),AND(L3&gt;1,L3&lt;&gt;"-"),AND(M3&gt;1,M3&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>2015</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>4</v>
+        <v>41</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="17">
         <v>1</v>
       </c>
-      <c r="J4" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4" s="21" t="str">
-        <f>IF(OR(AND(I4&gt;1,I4&lt;&gt;"-"),AND(J4&gt;1,J4&lt;&gt;"-"),AND(K4&gt;1,K4&lt;&gt;"-")),"Can exchange","")</f>
+      <c r="L4" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="21" t="str">
+        <f t="shared" ref="N4:N20" si="0">IF(OR(AND(J4&gt;1,J4&lt;&gt;"-"),AND(K4&gt;1,K4&lt;&gt;"-"),AND(L4&gt;1,L4&lt;&gt;"-"),AND(M4&gt;1,M4&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19">
         <v>2015</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>27</v>
+        <v>41</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>4</v>
@@ -1327,36 +1382,42 @@
       <c r="H5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="17">
         <v>1</v>
       </c>
-      <c r="J5" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="21" t="str">
-        <f>IF(OR(AND(I5&gt;1,I5&lt;&gt;"-"),AND(J5&gt;1,J5&lt;&gt;"-"),AND(K5&gt;1,K5&lt;&gt;"-")),"Can exchange","")</f>
+      <c r="N5" s="21" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19">
         <v>2015</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>4</v>
@@ -1364,114 +1425,132 @@
       <c r="H6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="17">
         <v>1</v>
       </c>
-      <c r="J6" s="17" t="s">
-        <v>4</v>
-      </c>
       <c r="K6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="21" t="str">
-        <f>IF(OR(AND(I6&gt;1,I6&lt;&gt;"-"),AND(J6&gt;1,J6&lt;&gt;"-"),AND(K6&gt;1,K6&lt;&gt;"-")),"Can exchange","")</f>
+      <c r="L6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N6" s="21" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19">
         <v>2016</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J7" s="17">
+      <c r="I7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="17">
         <v>1</v>
       </c>
-      <c r="K7" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="21" t="str">
-        <f t="shared" ref="L7:L13" si="0">IF(OR(AND(I7&gt;1,I7&lt;&gt;"-"),AND(J7&gt;1,J7&lt;&gt;"-"),AND(K7&gt;1,K7&lt;&gt;"-")),"Can exchange","")</f>
+      <c r="L7" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="21" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19">
         <v>2016</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="17">
+      <c r="I8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="17">
         <v>2</v>
       </c>
-      <c r="K8" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="21" t="str">
+      <c r="L8" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19">
         <v>2017</v>
       </c>
       <c r="B9" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>42</v>
-      </c>
       <c r="F9" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>4</v>
@@ -1479,38 +1558,44 @@
       <c r="H9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="17">
         <v>1</v>
       </c>
-      <c r="J9" s="17" t="s">
-        <v>4</v>
-      </c>
       <c r="K9" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L9" s="21" t="str">
+      <c r="L9" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19">
         <v>2017</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>4</v>
@@ -1518,85 +1603,97 @@
       <c r="H10" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="17">
         <v>1</v>
       </c>
-      <c r="J10" s="17" t="s">
-        <v>4</v>
-      </c>
       <c r="K10" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="21" t="str">
+      <c r="L10" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19">
         <v>2018</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="17">
+      <c r="I11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="17">
         <v>1</v>
       </c>
-      <c r="K11" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="21" t="str">
+      <c r="L11" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N11" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19">
         <v>2018</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>21</v>
+        <v>41</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J12" s="17">
@@ -1605,103 +1702,121 @@
       <c r="K12" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="L12" s="21" t="str">
+      <c r="L12" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19">
         <v>2019</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="6" t="s">
         <v>4</v>
       </c>
       <c r="J13" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="17">
         <v>1</v>
       </c>
-      <c r="L13" s="21" t="str">
+      <c r="M13" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N13" s="21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19">
         <v>2020</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="17">
+      <c r="I14" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="17">
         <v>1</v>
       </c>
-      <c r="K14" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="L14" s="21" t="str">
-        <f>IF(OR(AND(I14&gt;1,I14&lt;&gt;"-"),AND(J14&gt;1,J14&lt;&gt;"-"),AND(K14&gt;1,K14&lt;&gt;"-")),"Can exchange","")</f>
+      <c r="L14" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="21" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="19">
         <v>2021</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>4</v>
@@ -1709,199 +1824,327 @@
       <c r="H15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="17">
         <v>1</v>
       </c>
-      <c r="J15" s="17" t="s">
-        <v>4</v>
-      </c>
       <c r="K15" s="17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L15" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19">
         <v>2022</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="17">
+      <c r="I16" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K16" s="17">
         <v>1</v>
       </c>
-      <c r="K16" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L16" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19">
         <v>2022</v>
       </c>
       <c r="B17" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="H17" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="17">
+      <c r="I17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="17">
         <v>1</v>
       </c>
-      <c r="K17" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L17" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19">
         <v>2023</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="17">
+      <c r="G18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="17">
         <v>1</v>
       </c>
-      <c r="K18" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M18" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="19">
         <v>2024</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="17">
+      <c r="G19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="17">
         <v>1</v>
       </c>
-      <c r="K19" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M19" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19">
         <v>2025</v>
       </c>
       <c r="B20" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="H20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="17">
+      <c r="I20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="17">
         <v>1</v>
       </c>
-      <c r="K20" s="17" t="s">
-        <v>4</v>
+      <c r="L20" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B2:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J12 K14 I7:J11 K7:K12 I3:K6">
-    <cfRule type="containsText" dxfId="26" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K14 J12 I7:J11 K7:K12 I3:K6">
+  <conditionalFormatting sqref="L14 J7:K11 L7:L12 K12 J3:M6 M7:M20">
+    <cfRule type="containsText" dxfId="26" priority="71" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:K11 L14 L7:L12 K12 J3:M6 M7:M20">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
+    <cfRule type="containsText" dxfId="25" priority="67" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14:K14">
+    <cfRule type="containsText" dxfId="24" priority="65" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14:K14">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L13">
+    <cfRule type="containsText" dxfId="23" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L13">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="containsText" dxfId="22" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1913,29 +2156,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="25" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="24" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
+  <conditionalFormatting sqref="K15">
+    <cfRule type="containsText" dxfId="21" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K15">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1947,12 +2173,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J14">
-    <cfRule type="containsText" dxfId="23" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I14:J14">
+  <conditionalFormatting sqref="L15">
+    <cfRule type="containsText" dxfId="20" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L15">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1964,12 +2190,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="22" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
+  <conditionalFormatting sqref="J16">
+    <cfRule type="containsText" dxfId="19" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1981,13 +2207,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="21" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J13">
-    <cfRule type="colorScale" priority="52">
+  <conditionalFormatting sqref="L16">
+    <cfRule type="containsText" dxfId="18" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L16">
+    <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1998,12 +2224,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
-    <cfRule type="containsText" dxfId="20" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J15">
+  <conditionalFormatting sqref="J17">
+    <cfRule type="containsText" dxfId="17" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2015,29 +2241,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K15">
-    <cfRule type="containsText" dxfId="19" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K15">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16">
-    <cfRule type="containsText" dxfId="18" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16">
+  <conditionalFormatting sqref="L17">
+    <cfRule type="containsText" dxfId="16" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L17">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2049,13 +2258,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="17" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="colorScale" priority="40">
+  <conditionalFormatting sqref="J18">
+    <cfRule type="containsText" dxfId="15" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J18">
+    <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2066,13 +2275,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="16" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="colorScale" priority="38">
+  <conditionalFormatting sqref="J15">
+    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J15">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2083,12 +2292,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K17">
-    <cfRule type="containsText" dxfId="15" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K17">
+  <conditionalFormatting sqref="K16">
+    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
     <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2100,12 +2309,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
-    <cfRule type="containsText" dxfId="14" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
+  <conditionalFormatting sqref="K17">
+    <cfRule type="containsText" dxfId="12" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K17">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2117,63 +2326,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K18">
-    <cfRule type="containsText" dxfId="13" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K18">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="12" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17">
-    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J17">
+  <conditionalFormatting sqref="J20">
+    <cfRule type="containsText" dxfId="11" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J20">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2185,12 +2343,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J18">
-    <cfRule type="containsText" dxfId="9" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J18">
+  <conditionalFormatting sqref="L20">
+    <cfRule type="containsText" dxfId="10" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2202,13 +2360,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="K20">
+    <cfRule type="containsText" dxfId="9" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2219,12 +2377,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K20">
+  <conditionalFormatting sqref="J19">
+    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12">
     <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K20">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2236,12 +2411,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J20">
+  <conditionalFormatting sqref="L18">
     <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J20">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L18">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2253,12 +2428,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I19">
+  <conditionalFormatting sqref="L19">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I19">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2270,12 +2445,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K19">
+  <conditionalFormatting sqref="K18">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K19">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K18">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2287,12 +2462,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J19">
+  <conditionalFormatting sqref="K19">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J19">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K19">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
